--- a/data/roster.xlsx
+++ b/data/roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TanguyVY\Dropbox\jeux pedagogique\cournot-pilote\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC1FBB24-1DA3-4F7B-8BF2-4F0F7819C81F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFBA459-7B27-4C72-BBFF-B2D1D8B21BE3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -34,15 +34,6 @@
     <t>Paul</t>
   </si>
   <si>
-    <t>De Grauwe</t>
-  </si>
-  <si>
-    <t>Mathias</t>
-  </si>
-  <si>
-    <t>Dewatripont</t>
-  </si>
-  <si>
     <t>Jean</t>
   </si>
   <si>
@@ -155,6 +146,9 @@
   </si>
   <si>
     <t>d'Aspremont</t>
+  </si>
+  <si>
+    <t>Belleflamme</t>
   </si>
 </sst>
 </file>
@@ -494,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -516,7 +510,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -524,10 +518,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -535,10 +529,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -546,10 +540,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -557,10 +551,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -568,10 +562,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -579,10 +573,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -590,10 +584,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -601,10 +595,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -612,10 +606,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -623,10 +617,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -634,10 +628,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -645,10 +639,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -656,10 +650,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -667,10 +661,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
         <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -678,10 +672,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -689,10 +683,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -700,10 +694,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -711,10 +705,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -722,10 +716,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -733,21 +727,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
